--- a/docs/qa/export/excel/CREDENTIALS_LOG.xlsx
+++ b/docs/qa/export/excel/CREDENTIALS_LOG.xlsx
@@ -158,7 +158,7 @@
     <t>Item 4</t>
   </si>
   <si>
-    <t>Tables (API)</t>
+    <t>Tables (Admin)</t>
   </si>
   <si>
     <t>Table T1 ID</t>

--- a/docs/qa/export/excel/CREDENTIALS_LOG.xlsx
+++ b/docs/qa/export/excel/CREDENTIALS_LOG.xlsx
@@ -125,10 +125,10 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Waiter URL</t>
-  </si>
-  <si>
-    <t>https://waiter.cullinos.com</t>
+    <t>Waiter app</t>
+  </si>
+  <si>
+    <t>Cullinos Waiter Android</t>
   </si>
   <si>
     <t>Optional Cashier</t>
